--- a/tools/importer/reports/import-techdocs-release-notes.report.xlsx
+++ b/tools/importer/reports/import-techdocs-release-notes.report.xlsx
@@ -73,7 +73,7 @@
     <t>techdocs-release-notes</t>
   </si>
   <si>
-    <t>2026-07-17T16:11:17.939Z</t>
+    <t>2026-07-17T23:53:52.112Z</t>
   </si>
   <si>
     <t>VMware Tanzu Hub release notes</t>
